--- a/tmp/言語別SBOM生成方法と脆弱性検知手段_20261012_r3.xlsx
+++ b/tmp/言語別SBOM生成方法と脆弱性検知手段_20261012_r3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shuyo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80D3210-FCED-4043-8698-B2ED06AEAA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCED6006-F226-4976-853A-F23E299DE12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="1257">
   <si>
     <t>1. 考え方: まず SBOM で検知する。SBOM で検知できないものは、一万行リスト、AIスキャン、サーバスキャンで検知する</t>
   </si>
@@ -4772,6 +4772,11 @@
     <rPh sb="12" eb="14">
       <t>トクテイ</t>
     </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>一万行リストに手動追加
+AIスキャン</t>
     <phoneticPr fontId="15"/>
   </si>
 </sst>
@@ -6465,7 +6470,7 @@
         <v>73</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>67</v>
+        <v>1256</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>39</v>
@@ -6527,7 +6532,7 @@
         <v>77</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>67</v>
+        <v>1256</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>39</v>
@@ -6589,7 +6594,7 @@
         <v>78</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>67</v>
+        <v>1256</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>39</v>
